--- a/outputs/evaluation/decision/v1/CF_M01/run_1/CF_M01_decision_eval_llm_report.xlsx
+++ b/outputs/evaluation/decision/v1/CF_M01/run_1/CF_M01_decision_eval_llm_report.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J4"/>
+  <dimension ref="A1:J8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,146 +476,346 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>The platform is a web service that follows the client-server architecture, and for the client-server model, a 3-layer architecture is used, where the system is divided into 3 layers: the presentation layer, the business layer, and the data layer.</t>
+          <t>Aquestes tecnologies són les mateixes de les quals s’utilitzen actualment a l’empresa de Waapiti.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>C_05</t>
+          <t>Waapiti</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>P_01, P_02</t>
+          <t>AU_13, AU_14</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>8</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>15a. Access</t>
+          <t>Waapiti</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Client-Server; Layered Architecture</t>
+          <t>NestJS; TypeScript</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>CF_M01_AD06</t>
+          <t>CF_M01_AD07</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>In this project, this framework has been used to develop the different services that interact with each other. This framework allows the creation of a secure and complex REST API in an easier way than using NodeJS directly.</t>
+          <t>To ensure the fastest possible data transmission, two Amazon services have been used, which allow us to perform a transmission in almost real time.</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>0.6729000000000001</v>
+        <v>0.6361</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AD_06</t>
+          <t>AD_02</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>The objective of these services is to form a data lake where all history is stored to be able to process them in the analytical module.</t>
+          <t>Pel model client-servidor s’utilitza l’arquitectura de 3 capes, on el sistema es devidiex en 3 capes, la capa de presentació, la capa de negoci i la capa de dades.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>C_03, C_04</t>
+          <t>Client-Server</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>AU_12, AU_16</t>
+          <t>P_02, AU_03, AU_04, AU_05</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>41</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>12f. Capacity; 12g. Scalability</t>
+          <t>Client-Server</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cloud Storage Service; Amazon S3</t>
+          <t>Layered Architecture; Presentation Layer; Business Layer; Data Layer</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>CF_M01_AD01</t>
+          <t>CF_M01_AD06</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>The goal of this is to improve the security, scalability, and availability of the system.</t>
+          <t>In this project, this framework has been used to develop the different services that interact with each other. This framework allows the creation of a secure and complex REST API in an easier way than using NodeJS directly.</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>0.635</v>
+        <v>0.6347</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AD_07</t>
+          <t>AD_04</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Amazon Athena is a serverless service, which means it is not necessary to manage the infrastructure when there is an increase in the set of data and users. In addition, to obtain data quickly, Athena performs queries in parallel.</t>
+          <t>Aquest patró de disseny permet que solament un component sigui qui interactuï entre els usuaris i els serveis que proporciona la plataforma.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>C_01, Performance</t>
+          <t>Microservices API Gateway design pattern</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>AU_18</t>
+          <t>AU_06, P_03</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>43</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>12a. Speed and latency; Performance</t>
+          <t>Microservices API Gateway design pattern</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Amazon Athena</t>
+          <t>API Gateway Service; API Gateway</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
+          <t>CF_M01_AD06</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>In this project, this framework has been used to develop the different services that interact with each other. This framework allows the creation of a secure and complex REST API in an easier way than using NodeJS directly.</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>0.6549</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>AD_05</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Augmenta la seguretat del sistema al reduir les portes d’enllaç amb l’exterior, ja que l’única manera d’interactuar amb els microserveis és a través de l’Api Gateway.</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>AU_06, P_03</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>API Gateway Service; API Gateway</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>CF_M01_AD02</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Increases system security [...] It is only the Api Gateway that is responsible for authorization and SSL with the client</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>0.8393</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>AD_06</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Dona la capacitat de manegar caigudes parcials del sistema, manegant quins serveis estan en funcionament en tot moment.</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Availability and reliability</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>AU_06, P_03</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Availability and reliability</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>API Gateway Service; API Gateway</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>CF_M01_AD03</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Gives the ability to handle partial system crashes</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>0.7309</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>AD_08</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Aquesta base de dades està implementada en el servei RDS , que és un servei de base de dades relacional distribuït d’AWS.</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>RDS</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>AU_11</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>RDS</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Database</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
           <t>CF_M01_AD07</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>To ensure the fastest possible data transmission, two Amazon services have been used, which allow us to perform a transmission in almost real time.</t>
         </is>
       </c>
-      <c r="J4" t="n">
-        <v>0.6741</v>
+      <c r="J7" t="n">
+        <v>0.6366000000000001</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>AD_10</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Aquesta funció ens permet crear particions en S3, i d’aquesta manera crear subcarpetes, respecte a unes claus predefinides.</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>S3</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>AU_21</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>S3</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Kinesis Data Firehose</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>CF_M01_AD07</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>To ensure the fastest possible data transmission, two Amazon services have been used, which allow us to perform a transmission in almost real time.</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>0.5784</v>
       </c>
     </row>
   </sheetData>
